--- a/DS3D_HVAC_Variable_List.xlsx
+++ b/DS3D_HVAC_Variable_List.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="HVAC_Variables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Inbound_Commands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Outbound_Telemetry" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fault_Catalog" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +38,13 @@
       <name val="Segoe UI"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,8 +57,14 @@
         <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -72,11 +86,25 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -85,6 +113,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1030,4 +1073,1395 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="110" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>SR.No</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Command Name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>JSON Payload / Format</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Raw String Fallback</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Description &amp; Unity Behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Trigger Fault</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 101}</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Fault Control</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Starts procedural fault, focuses camera, highlights tool for Step 1. Cleanly resets prior fault if active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Trigger Fault (Shorthand)</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>{"fault": 101}</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Fault Control</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Equivalent shorthand to start a procedural fault scenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Reset Simulator</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "reset"}</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>reset</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Workflow Control</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Aborts active fault workflow, returns 3D tools, returns to idle 3D inspection state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Skip Current Step</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "skip_step"}</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Training Control</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Skips the active step forward during training / easy mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Airflow Speeds Telemetry</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>{"Hvac": {"Speed": [{"Name": "Fan1", "Value": 5.0}, ...]}}</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>CSV floats</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Animation / Sliders</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Continuous speed controls for fans and airflow arrows (0.0 to 10.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Color Intensity &amp; Dampers</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>{"Hvac": {"Amplitude": [{"Name": "FADL", "Value": 5.0}, ...]}}</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>CSV floats</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Animation / Sliders</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Controls blendshape positions for FADL/FADR/RAD dampers and arrow color lerps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>System Control Booleans</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>{"Hvac": {"Boolean": [{"Name": "ShowHideObjects", "Value": false}]}}</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>CSV 0/1</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>System Control</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Toggles component visibility (ShowHideObjects) or application termination (Application Quit).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="94" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>SR.No</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>JSON Tag / Key</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>LabVIEW Data Type</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Trigger Condition</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Network Behavior &amp; Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>step_completed</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Right tool used &amp; step finished</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Always "step_completed"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>step_completed</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>fault_code</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Numeric (I32)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Right tool used &amp; step finished</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>The active fault code being performed (e.g., 101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>step_completed</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>step_number</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Numeric (I32)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Right tool used &amp; step finished</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>1-based index of accomplished step (1, 2, 3...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>step_completed</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>wrong_attempts</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Numeric (I32)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Right tool used &amp; step finished</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Count of incorrect tool attempts made before completing this step (0, 1, 2...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>step_completed</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>total_steps</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Numeric (I32)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Right tool used &amp; step finished</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Total steps required in this fault procedure (e.g. 14 for Fault 101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>step_completed</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Right tool used &amp; step finished</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Execution status (always "success")</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>step_completed</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>is_fault_completed</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Right tool used &amp; step finished</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>true if this was the final step; otherwise false</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>fault_completed</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>All steps in fault finished</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Always "fault_completed"</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>fault_completed</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>fault_code</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Numeric (I32)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>All steps in fault finished</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Completed fault scenario code (e.g. 101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>fault_completed</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>All steps in fault finished</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Always "success"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>fault_completed</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>total_steps</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Numeric (I32)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>All steps in fault finished</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Total count of steps completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>fault_completed</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>wrong_attempts_per_step</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>1D Array of I32</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>All steps in fault finished</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Full sequence of wrong attempts per step, e.g. [0, 2, 1, 0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>fault_completed</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>is_fault_completed</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>All steps in fault finished</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Always true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>fault_started</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Fault started (Network or UI)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Always "fault_started"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>fault_started</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>fault_code</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Numeric (I32)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Fault started (Network or UI)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Fault scenario code being opened (e.g. 101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>fault_started</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>total_steps</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Numeric (I32)</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Fault started (Network or UI)</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Total step count for the initiated fault</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>fault_started</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Fault started (Network or UI)</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Always "started"</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Wrong Tool Rule</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>(No UDP Packet Sent)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Wrong tool clicked</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>SILENT on network. Unity displays error on 3D UI and increments wrong attempts internally.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Fault Code</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Subsystem</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Fault Title / Description</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Step Count</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Trigger Command</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>LabVIEW Cluster Mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Refrigeration Circuit</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>No HVAC operations</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 101}</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=101, total_steps=14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Blower &amp; Ventilation</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>No ventilation</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 102}</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=102, total_steps=22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Ventilation Circuit</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Reduced ventilation</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 103}</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=103, total_steps=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Compressor / Refrigerant</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Suction low and discharge low</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 104}</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=104, total_steps=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Expansion / Pressure</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Suction low and discharge low (Circuit 2)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 105}</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=105, total_steps=14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Pressure Differential</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>High suction and high discharge</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 106}</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=106, total_steps=26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Compressor Unit</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Compressor not operating</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 107}</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=107, total_steps=40</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Cooling Capacity</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Reduced cooling</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 108}</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=108, total_steps=33</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Heating Subsystem</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>No Heating</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 109}</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=109, total_steps=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Thermal Regulation</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Over Cooling</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 110}</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=110, total_steps=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Thermal Regulation</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Over Heating</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 111}</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=111, total_steps=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Emergency Systems</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>No emergency ventilation</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 112}</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=112, total_steps=14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Safety / Sensors</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Smoke identified in saloon</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 113}</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=113, total_steps=13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Mechanical Diagnostics</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Compressor excessively noisy | Condenser Fan or Supply Blower</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>{"command": "trigger_fault", "fault_code": 114}</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Cluster: fault_code=114, total_steps=36</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>